--- a/data/source/2026-09-28/BSR_FR_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
+++ b/data/source/2026-09-28/BSR_FR_Wet-Dry-Floor-Washer_Top50_2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="141">
   <si>
     <t>#</t>
   </si>
@@ -232,40 +232,181 @@
     <t>B0H69GTK93</t>
   </si>
   <si>
-    <t>https://www.amazon.frundefined</t>
+    <t>Marque: Generic | Caractéristique spéciale: Sans fil | Type de filtre: Filtre HEPA | Recommandation de surface: Maison | Source d'alimentation: Alimenté par batterie | Composants inclus: Accessoires pour sols durs, moquettes et tissus | Sans fil ?: Oui | Capacité: 1,5 litres | Utilisations recommandées pour le produit: Sols durs, moquettes, tissus, escaliers, voitures | Facteur de forme: Bâton</t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Generic</t>
   </si>
   <si>
     <t>Aspirateur sans Fil 50000Pa 600W 60Min Autonomie Grand Bac À Poussière Filtration 8 Étages pour Maison Poils Animaux</t>
   </si>
   <si>
+    <t xml:space="preserve">Puissance D’aspiration 50000Pa - Moteur Haute Performance Produisant 50000Pa D’aspiration Élimine La Poussière Profonde Les Acariens Et Les Poils D’animaux
+Moteur 600W Haute Efficacité - Moteur Numérique De 600W Offre Une Efficacité Énergétique Constante Sur Tous Les Types De Sols
+60 Minutes D’autonomie - Batterie Haute Capacité Assure Jusqu’à 60 Minutes De Nettoyage En Continu Idéal Pour Les Grandes Surfaces
+Filtration À 8 Étages - Système De Filtration Avancé Avec Filtre Hepa Capture 99.99% Des Particules Fines Et Allergènes
+Grand Bac À Poussière - Capacité De 1.5 Litres Réduit Les Vidages Fréquents Pratique Pour Les Grands Ménages</t>
+  </si>
+  <si>
     <t>https://www.amazon.fr/dp/B0H69GTK93?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/710l9PXoMvL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://m.media-amazon.com/images/I/41GgMUG408L._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs eau et poussière à usage domestique</t>
+  </si>
+  <si>
+    <t>Voir les 100 premiers en Cuisine et Maison</t>
+  </si>
+  <si>
+    <t>Aspirateurs eau et poussière à usage domestique</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>CHENMW Department Store</t>
+  </si>
+  <si>
+    <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQBFEG6BI2O00</t>
+  </si>
+  <si>
+    <t>4,46 Kilograms</t>
+  </si>
+  <si>
+    <t>4.46 kg</t>
+  </si>
+  <si>
+    <t>12L x 7l x 18H centimètres</t>
   </si>
   <si>
     <t>B0G7GJZ7WQ</t>
   </si>
   <si>
-    <t>JONR Aspirateur Eau et poussière 20 000 Pa H2, Design innovant sans Odeur, réservoir d'eau Extra Large de 1500 ML avec Plat à</t>
+    <t>Marque: JONR | Tension: 22 Volts | Sans fil ?: Oui | Poids de l'article: 3,5 Kilogrammes | Capacité: 1500 ml | Puissance en watts: 230 Watts | Temps de charge: 3 heures | Couleur: Noir | Dimensions du produit: 33L x 32l x 110H centimètres | Niveau sonore: 60 Décibels</t>
+  </si>
+  <si>
+    <t>JONR</t>
+  </si>
+  <si>
+    <t>https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0H3NZP2VD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>JONR Aspirateur Eau et poussière 20 000 Pa H2, Design innovant sans Odeur, réservoir d'eau Extra Large de 1500 ML avec Plat à 180° (Puissance d'aspiration et Puissance d'eau Non réduites). (S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design innovant sans odeur avec réservoir d'eau sale placé en bas : l'aspirateur eau et poussière JONR H2 convainc par son design innovant sans odeur avec réservoir d'eau sale intégré en bas. Il élimine durablement les odeurs désagréables qui apparaissent dans les appareils traditionnels après une utilisation prolongée. Le réservoir d'eau sale se démonte facilement et se rince directement pour une absence durable d'odeurs.
+Puissance d'aspiration de 20 000 Pa et plat à 180 ° : l'aspirateur eau et poussière JONR H2 offre une forte puissance d'aspiration de 20 000 Pa, bien plus que l'ED12 Pro Max avec 17 000 Pa. Même à 180 °, la puissance d'aspiration et le volume utile du réservoir d'eau douce restent complètement inchangés. Contrairement aux appareils traditionnels, où la puissance d'aspiration diminue et le réservoir d'eau douce ne peut être utilisé qu'à moitié, le H2 résout parfaitement ce problème.
+Longue durée de vie de 45 minutes et mode salle de bain : l'aspirateur sec et humide JONR H2 dispose d'un mode exclusif de salle de bain qui renforce considérablement les performances d'absorption d'eau et de séchage pour la cuisine, la salle de bain, la piscine et d'autres zones humides, pour un nettoyage à sec unique sans résidus. La batterie de 2600 mAh garantit une longue autonomie allant jusqu'à 45 minutes.
+Réservoir d'eau douce de 1500 ml et réservoir d'eau sale de 600 ml : le JONR H2 dispose d'un réservoir d'eau douce extra large de 1500 ml – deux fois plus grand que les appareils traditionnels (750 ml). Avec le réservoir d'eau sale de 600 ml, il permet une surface de nettoyage de plus de 300 m² par remplissage. Plus besoin de remplir fréquemment l'eau pour un nettoyage efficace et sans interruption.
+Design de nettoyage extrême à 3 bords et technologie anti-enroulement des poils 3.0 : le design à 3 bords bien pensé permet un nettoyage parfait même dans les coins et les bords. La technologie anti-enroulement des cheveux 3.0 résout à 100 % le problème de l'enchevêtrement des cheveux (données du laboratoire JONR). Le JONR H2 est votre assistant idéal pour la maison quotidienne.</t>
   </si>
   <si>
     <t>https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0GSZCMGCG</t>
+  </si>
+  <si>
+    <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs balais et balais électriques</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>JONR Official</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>苏州市 江苏 215028 CN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1R6H4HF5LIC6Y</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>3,5 Kilogrammes</t>
+  </si>
+  <si>
+    <t>33L x 32l x 110H centimètres</t>
+  </si>
+  <si>
+    <t>6.78 kg</t>
+  </si>
+  <si>
+    <t>61 x 33.8 x 32.3 cm</t>
+  </si>
+  <si>
+    <t>61.00 x 33.80 x 32.30 cm</t>
+  </si>
+  <si>
+    <t>轻型标准大件</t>
   </si>
   <si>
     <t>B0GL7P6391</t>
   </si>
   <si>
-    <t>JONR Aspirateur sans fil avec eau chaude auto-nettoyante, design innovant de protection contre les odeurs, aspiration ouragan</t>
+    <t>Marque: JONR | Caractéristique spéciale: Duo-Clean | Type de filtre: Élément filtrant en éponge | Recommandation de surface: Tous étage confondu | Source d'alimentation: Alimenté par batterie | Tension: 20.0 | Composants inclus: Batterie | Sans fil ?: Non | Poids de l'article: 7,9 Livres | Capacité: 1500 milligrammes</t>
+  </si>
+  <si>
+    <t>https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+  </si>
+  <si>
+    <t>JONR Aspirateur sans fil avec eau chaude auto-nettoyante, design innovant de protection contre les odeurs, aspiration ouragan 20 000 Pa, 180 ° à plat sans perte de puissance et de capacité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONR Aspirateur humide et sec H2 PRO (version améliorée du H2 – En s'appuyant sur les caractéristiques du H2, la fonction autonettoyante d'eau chaude à 70 °C et la fonction de séchage à l'air chaud ont été ajoutées. L'eau chaude autonettoyante à 70 °C élimine en profondeur les taches tenaces. Il utilise une méthode de séchage localisée unique, flexible, qui diffère de la rotation traditionnelle à grande vitesse. Notre méthode innovante prolonge considérablement la durée de vie du moteur et atteint un taux de séchage allant jusqu'à 90 %
+Design innovant sans odeur avec réservoir d'eau sale monté par le bas : l'aspirateur sec/humide JONR H2 Pro dispose d'un design innovant sans odeur avec un réservoir d'eau sale intégré au fond. Cela élimine définitivement les odeurs désagréables qui peuvent se développer avec les aspirateurs conventionnels après une utilisation prolongée. Le réservoir d'eau sale est facile à enlever et à rincer directement, assurant un fonctionnement durable sans odeur.
+Puissance d'aspiration de 20 000 Pa et positionnement à plat à 180° - L'aspirateur sec/humide JONR H2 PRO offre une aspiration puissante de 20 000 Pa, soit bien plus que l'aspirateur ED12 PRO MAX avec 17 000 Pa. Même à plat à 180°, la puissance d'aspiration et le volume utile du réservoir d'eau douce restent complètement inchangés. Contrairement aux appareils classiques où la puissance d'aspiration diminue et où le réservoir d'eau douce ne peut être utilisé qu'à mi-chemin, le H2 PRO résout parfaitement ce problème.
+Modl d'autonomie et de salle de bain de 45 minutes : l'aspirateur humide/sec JONR H2 PRO dispose d'un mode salle de bain exclusif qui améliore considérablement les performances de collecte et de séchage de l'eau pour les cuisines, les salles de bains, les piscines et autres zones humides – pour un nettoyage à sec unique et sans résidus. La batterie de 2600 mAh garantit une longue autonomie allant jusqu'à 45 minutes.
+Réservoir d'eau douce de 1500 ml et réservoir d'eau sale de 600 ml – Le JONR H2 Pro dispose d'un réservoir d'eau douce extra large de 1500 ml – deux fois la taille des appareils conventionnels (750 ml). Avec le réservoir d'eau sale de 600 ml, il permet une surface de nettoyage de plus de 300 m² par cycle de remplissage. Le remplissage fréquent est éliminé pour un nettoyage efficace et ininterrompu.</t>
   </si>
   <si>
     <t>https://www.amazon.fr/dp/B0GL7P6391?psc=1</t>
   </si>
   <si>
-    <t>https://images-eu.ssl-images-amazon.com/images/I/61XGdRmjoeL._AC_UL300_SR300,200_.jpg</t>
+    <t>https://images-na.ssl-images-amazon.com/images/I/61beLprTKNL._AC_US600_.jpg</t>
+  </si>
+  <si>
+    <t>B0GWRWCTS1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>7,9 Livres</t>
+  </si>
+  <si>
+    <t>27L x 21l x 110H centimètres</t>
+  </si>
+  <si>
+    <t>7.98 kg</t>
+  </si>
+  <si>
+    <t>61.7 x 34.5 x 33 cm</t>
+  </si>
+  <si>
+    <t>61.70 x 34.50 x 33.00 cm</t>
   </si>
   <si>
     <t>导出时自动对相同ASIN去重。可能导致导出的产品总数与页面显示数量不一致</t>
@@ -281,9 +422,6 @@
   </si>
   <si>
     <t>市场份额</t>
-  </si>
-  <si>
-    <t>未知品牌</t>
   </si>
   <si>
     <t>卖家</t>
@@ -458,6 +596,9 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -484,9 +625,6 @@
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -569,13 +707,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -613,13 +751,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1304,44 +1442,46 @@
         <v>70</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="14" t="s">
+        <v>79</v>
+      </c>
       <c r="N2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O2" s="15">
+        <v>621749</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>0</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="S2" s="18" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="T2" s="15" t="s">
         <v>70</v>
@@ -1358,22 +1498,38 @@
       <c r="X2" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="4"/>
+      <c r="Y2" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="20">
+        <v>39.99</v>
+      </c>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="2"/>
       <c r="AD2" s="19">
         <v>1</v>
       </c>
-      <c r="AF2" s="20">
+      <c r="AE2" s="15">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="21">
         <v>4</v>
       </c>
-      <c r="AG2" s="21">
+      <c r="AG2" s="22">
         <v>0</v>
       </c>
       <c r="AI2" s="16">
         <v>0</v>
       </c>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="19" t="s">
-        <v>70</v>
+      <c r="AK2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL2" s="19">
+        <v>78</v>
+      </c>
+      <c r="AM2" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="AN2" s="13" t="s">
         <v>70</v>
@@ -1381,9 +1537,19 @@
       <c r="AO2" s="13" t="s">
         <v>70</v>
       </c>
+      <c r="AP2" s="4"/>
       <c r="AQ2" s="19" t="s">
         <v>70</v>
       </c>
+      <c r="AR2" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT2" s="13" t="s">
+        <v>84</v>
+      </c>
       <c r="AU2" s="13" t="s">
         <v>70</v>
       </c>
@@ -1391,7 +1557,7 @@
         <v>70</v>
       </c>
       <c r="AW2" s="13" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="AX2" s="13" t="s">
         <v>70</v>
@@ -1426,20 +1592,26 @@
       <c r="BH2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ2" s="22" t="s">
+      <c r="BJ2" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK2" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="BL2" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="BM2" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BO2" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BQ2" s="23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1447,44 +1619,47 @@
         <v>70</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>70</v>
+        <v>91</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>99</v>
+      </c>
       <c r="N3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="O3" s="15">
+        <v>1076803</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="16">
+        <v>0</v>
       </c>
       <c r="R3" s="17" t="s">
         <v>70</v>
@@ -1507,22 +1682,41 @@
       <c r="X3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="Z3" s="4"/>
+      <c r="Y3" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>199.99</v>
+      </c>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="2"/>
       <c r="AD3" s="19">
-        <v>49</v>
-      </c>
-      <c r="AF3" s="20">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="21">
         <v>3.5</v>
       </c>
-      <c r="AG3" s="21">
-        <v>0</v>
+      <c r="AG3" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>10.27</v>
       </c>
       <c r="AI3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="19" t="s">
-        <v>70</v>
+        <v>0.8</v>
+      </c>
+      <c r="AK3" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL3" s="19">
+        <v>192</v>
+      </c>
+      <c r="AM3" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="AN3" s="13" t="s">
         <v>70</v>
@@ -1530,17 +1724,27 @@
       <c r="AO3" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ3" s="19" t="s">
-        <v>70</v>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR3" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="AT3" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="AU3" s="13" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="AV3" s="14" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="AW3" s="13" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="AX3" s="13" t="s">
         <v>70</v>
@@ -1558,16 +1762,16 @@
         <v>70</v>
       </c>
       <c r="BC3" s="13" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="BD3" s="13" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="BE3" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BF3" s="13" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="BG3" s="13" t="s">
         <v>70</v>
@@ -1575,20 +1779,35 @@
       <c r="BH3" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ3" s="22" t="s">
-        <v>70</v>
+      <c r="BJ3" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="BK3" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="BM3" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN3" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO3" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="BP3" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="BQ3" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="BR3" s="13" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" ht="24" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1596,50 +1815,53 @@
         <v>70</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="14" t="s">
+      <c r="O4" s="15">
+        <v>1901494</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="16">
+        <v>0</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>70</v>
-      </c>
       <c r="S4" s="18" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="T4" s="15" t="s">
         <v>70</v>
@@ -1656,22 +1878,39 @@
       <c r="X4" s="15" t="s">
         <v>70</v>
       </c>
+      <c r="Y4" s="19">
+        <v>1</v>
+      </c>
       <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="2"/>
       <c r="AD4" s="19">
         <v>37</v>
       </c>
-      <c r="AF4" s="20">
+      <c r="AE4" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="21">
         <v>3.3</v>
       </c>
-      <c r="AG4" s="21">
-        <v>0</v>
+      <c r="AG4" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="20">
+        <v>10.48</v>
       </c>
       <c r="AI4" s="16">
         <v>0</v>
       </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="19" t="s">
-        <v>70</v>
+      <c r="AK4" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL4" s="19">
+        <v>157</v>
+      </c>
+      <c r="AM4" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="AN4" s="13" t="s">
         <v>70</v>
@@ -1679,8 +1918,14 @@
       <c r="AO4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AQ4" s="19" t="s">
-        <v>70</v>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="1"/>
+      <c r="AT4" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="AU4" s="13" t="s">
         <v>70</v>
@@ -1724,120 +1969,143 @@
       <c r="BH4" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BK4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BM4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BO4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ4" s="22" t="s">
-        <v>70</v>
+      <c r="BJ4" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="BK4" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BL4" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="BM4" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN4" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="BO4" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="BP4" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ4" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR4" s="13" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="23"/>
-      <c r="AK5" s="23"/>
-      <c r="AL5" s="24"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="24"/>
-      <c r="AR5" s="24"/>
-      <c r="AS5" s="23"/>
-      <c r="AT5" s="23"/>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="23"/>
-      <c r="AX5" s="23"/>
-      <c r="AY5" s="23"/>
-      <c r="AZ5" s="23"/>
-      <c r="BA5" s="23"/>
-      <c r="BB5" s="23"/>
-      <c r="BC5" s="23"/>
-      <c r="BD5" s="23"/>
-      <c r="BE5" s="23"/>
-      <c r="BF5" s="23"/>
-      <c r="BG5" s="23"/>
-      <c r="BH5" s="23"/>
-      <c r="BI5" s="23"/>
-      <c r="BJ5" s="23"/>
-      <c r="BK5" s="23"/>
-      <c r="BL5" s="23"/>
-      <c r="BM5" s="23"/>
-      <c r="BN5" s="23"/>
-      <c r="BO5" s="23"/>
-      <c r="BP5" s="23"/>
-      <c r="BQ5" s="23"/>
-      <c r="BR5" s="23"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="26"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="25"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="24"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="24"/>
+      <c r="AT5" s="24"/>
+      <c r="AU5" s="24"/>
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="24"/>
+      <c r="AX5" s="24"/>
+      <c r="AY5" s="24"/>
+      <c r="AZ5" s="24"/>
+      <c r="BA5" s="24"/>
+      <c r="BB5" s="24"/>
+      <c r="BC5" s="24"/>
+      <c r="BD5" s="24"/>
+      <c r="BE5" s="24"/>
+      <c r="BF5" s="24"/>
+      <c r="BG5" s="24"/>
+      <c r="BH5" s="24"/>
+      <c r="BI5" s="24"/>
+      <c r="BJ5" s="24"/>
+      <c r="BK5" s="24"/>
+      <c r="BL5" s="24"/>
+      <c r="BM5" s="24"/>
+      <c r="BN5" s="24"/>
+      <c r="BO5" s="24"/>
+      <c r="BP5" s="24"/>
+      <c r="BQ5" s="24"/>
+      <c r="BR5" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" tooltip="https://www.amazon.fr/dp/B0H69GTK93"/>
-    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="G2" r:id="rId2" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Generic"/>
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.fr/dp/B0H69GTK93?psc=1"/>
-    <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710l9PXoMvL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="K2" r:id="rId4" tooltip="https://m.media-amazon.com/images/I/41GgMUG408L._AC_US600_.jpg"/>
     <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.fr/dp/B0H69GTK93"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.fr/dp/B0GL7P6391"/>
-    <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.fr/dp/B0GL7P6391?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61XGdRmjoeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.fr/dp/B0GL7P6391"/>
+    <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.fr/b?node=218877814031"/>
+    <hyperlink ref="N2" r:id="rId7"/>
+    <hyperlink ref="AW2" r:id="rId8" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AQBFEG6BI2O00"/>
+    <hyperlink ref="C3" r:id="rId9" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="G3" r:id="rId10" tooltip="https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0H3NZP2VD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J3" r:id="rId11" tooltip="https://www.amazon.fr/dp/B0G7GJZ7WQ?psc=1"/>
+    <hyperlink ref="K3" r:id="rId12" tooltip="https://images-na.ssl-images-amazon.com/images/I/61ruaomVmXL._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId13" tooltip="https://www.amazon.fr/dp/B0GSZCMGCG"/>
+    <hyperlink ref="M3" r:id="rId14" tooltip="https://www.amazon.fr/b?node=3575230031"/>
+    <hyperlink ref="N3" r:id="rId15"/>
+    <hyperlink ref="AW3" r:id="rId16" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1R6H4HF5LIC6Y"/>
+    <hyperlink ref="C4" r:id="rId17" tooltip="https://www.amazon.fr/dp/B0GL7P6391"/>
+    <hyperlink ref="G4" r:id="rId18" tooltip="https://www.amazon.fr/stores/JONR/page/2E11CD6D-6ABC-4227-8074-804128923C6D?lp_asin=B0GL7P6391&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J4" r:id="rId19" tooltip="https://www.amazon.fr/dp/B0GL7P6391?psc=1"/>
+    <hyperlink ref="K4" r:id="rId20" tooltip="https://images-na.ssl-images-amazon.com/images/I/61beLprTKNL._AC_US600_.jpg"/>
+    <hyperlink ref="L4" r:id="rId21" tooltip="https://www.amazon.fr/dp/B0GWRWCTS1"/>
+    <hyperlink ref="M4" r:id="rId22" tooltip="https://www.amazon.fr/b?node=218877814031"/>
+    <hyperlink ref="N4" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -1857,21 +2125,21 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B2" s="15">
         <v>0</v>
@@ -1880,15 +2148,38 @@
         <v>0</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29">
-        <v>0</v>
-      </c>
-      <c r="G2" s="21">
+        <v>3159</v>
+      </c>
+      <c r="F2" s="20">
+        <v>39.99</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="15">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20">
+        <v>100</v>
+      </c>
+      <c r="G3" s="22">
         <v>0</v>
       </c>
     </row>
@@ -1900,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -1911,7 +2202,7 @@
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>19</v>
@@ -1920,21 +2211,21 @@
         <v>21</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B2" s="15">
         <v>0</v>
@@ -1943,15 +2234,61 @@
         <v>0</v>
       </c>
       <c r="D2" s="15">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E2" s="15">
-        <v>0</v>
-      </c>
-      <c r="F2" s="29">
-        <v>0</v>
-      </c>
-      <c r="G2" s="21">
+        <v>3159</v>
+      </c>
+      <c r="F2" s="20">
+        <v>39.99</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="15">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20">
+        <v>199.99</v>
+      </c>
+      <c r="G3" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="15">
+        <v>0</v>
+      </c>
+      <c r="C4" s="15">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="20">
+        <v>0</v>
+      </c>
+      <c r="G4" s="22">
         <v>0</v>
       </c>
     </row>
@@ -1971,37 +2308,37 @@
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:1" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:1" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
